--- a/website/examples/example_odk_gps_target_navigator.xlsx
+++ b/website/examples/example_odk_gps_target_navigator.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R63182823c3bc48c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R3f80a7c88e544345"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R46ddac33fe5e4c06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Ra2da3b7b40b744ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R9cb882d9cc4a40eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Rc198567fb76547be"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -461,7 +461,7 @@
         <x:v>field-list</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str">
-        <x:v>com.example.researchos.EXECUTE_METHOD(method_id='gps_target_navigator',input_target_latitude=${target_latitude_input},input_target_longitude=${target_longitude_input},input_arrival_radius_m=${arrival_radius_input})</x:v>
+        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='gps_target_navigator',input_target_latitude=${target_latitude_input},input_target_longitude=${target_longitude_input},input_arrival_radius_m=${arrival_radius_input})</x:v>
       </x:c>
       <x:c r="F5" s="11"/>
       <x:c r="G5" s="11"/>
@@ -473,10 +473,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>researchos_execution_id</x:v>
+        <x:v>methodmesh_execution_id</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>ResearchOS execution ID</x:v>
+        <x:v>MethodMesh execution ID</x:v>
       </x:c>
       <x:c r="D6" s="11"/>
       <x:c r="E6" s="11"/>
@@ -490,10 +490,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>researchos_status</x:v>
+        <x:v>methodmesh_status</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>ResearchOS status</x:v>
+        <x:v>MethodMesh status</x:v>
       </x:c>
       <x:c r="D7" s="11"/>
       <x:c r="E7" s="11"/>
@@ -801,7 +801,7 @@
         <x:v>2026072707</x:v>
       </x:c>
       <x:c r="D2" s="12" t="str">
-        <x:v>${researchos_status}</x:v>
+        <x:v>${methodmesh_status}</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/website/examples/example_odk_gps_target_navigator.xlsx
+++ b/website/examples/example_odk_gps_target_navigator.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>com.example.methodmesh.EXECUTE_METHOD(method_id='gps_target_navigator',input_target_name=${target_name_input},input_target_plus_code=${target_plus_code_input},input_target_latitude=${target_latitude_input},input_target_longitude=${target_longitude_input},input_arrival_radius_m=${arrival_radius_input},return_mode='flat')</t>
+          <t>com.example.methodmesh.EXECUTE_METHOD(method_id='gps_target_navigator',input_target_name=${target_name_input},input_target_plus_code=${target_plus_code_input},input_target_latitude=${target_latitude_input},input_target_longitude=${target_longitude_input},input_arrival_radius_m=${arrival_radius_input},input_payload_mode='FULL',return_mode='flat')</t>
         </is>
       </c>
     </row>
@@ -1004,27 +1004,49 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>navigation_summary</t>
+          <t>methodmesh_full_json</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Navigation: ${distance_m} m from ${target_name}; arrived=${arrived}</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>${methodmesh_status} != ''</t>
+          <t>MethodMesh metadata JSON</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>navigation_summary</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Navigation: ${distance_m} m from ${target_name}; arrived=${arrived}</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>${methodmesh_status} != ''</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>end_group</t>
         </is>
